--- a/src/attributions/attributions_ig_traj_499.xlsx
+++ b/src/attributions/attributions_ig_traj_499.xlsx
@@ -1002,43 +1002,43 @@
         <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.09990638128057558</v>
+        <v>-0.233280103660878</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2120382236287753</v>
+        <v>-0.1030879013646867</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01537492257737358</v>
+        <v>0.1129610349003072</v>
       </c>
       <c r="F2" t="n">
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.07541003767991721</v>
+        <v>-0.2338967862558475</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1924694857085359</v>
+        <v>0.07447873420358578</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02980939654462182</v>
+        <v>0.2342406226382536</v>
       </c>
       <c r="O2" t="n">
         <v>-0</v>
@@ -1047,31 +1047,31 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.112993313119286</v>
+        <v>-0.0002818106797719851</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01741763980473633</v>
+        <v>0.08045227092969286</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.05480521067106651</v>
+        <v>-0.04349659785533297</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -1080,28 +1080,28 @@
         <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.04763560623632488</v>
+        <v>0.04553665058145066</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.001231494748786342</v>
+        <v>0.01658115490219505</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.02180049073613898</v>
+        <v>-0.1009175651327652</v>
       </c>
       <c r="AG2" t="n">
         <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -1110,76 +1110,76 @@
         <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.017011889677344</v>
+        <v>-0.1522289740170924</v>
       </c>
       <c r="AM2" t="n">
         <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.01655520015105</v>
+        <v>-0.04025785631725773</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.08616768995696322</v>
+        <v>-0.3115529708167137</v>
       </c>
       <c r="AP2" t="n">
         <v>-0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.008540910523613702</v>
+        <v>0.03943941939144466</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.02384383279224323</v>
+        <v>0.05294703475172748</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.002653279452716468</v>
+        <v>0.001116873159024062</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC2" t="n">
         <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.05609398520719405</v>
+        <v>0.1056500781132248</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0901994727725183</v>
+        <v>-0.1187033396002762</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.03183116576526138</v>
+        <v>0.2227564019098115</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
         <v>-0</v>
@@ -1191,43 +1191,43 @@
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.01740503018763945</v>
+        <v>0.07190256250533789</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.04817202116933253</v>
+        <v>0.2382049193796306</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.0458225377765082</v>
+        <v>0.04939534417122356</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR2" t="n">
         <v>-0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
         <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.03495484539737654</v>
+        <v>-0.2556526958528827</v>
       </c>
       <c r="BW2" t="n">
         <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.0121282688106168</v>
+        <v>0.1846550387890183</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.01135934596789276</v>
+        <v>-0.006764130688894868</v>
       </c>
       <c r="BZ2" t="n">
         <v>-0</v>
@@ -1236,55 +1236,55 @@
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.02622384571045857</v>
+        <v>0.1716036536701028</v>
       </c>
       <c r="CF2" t="n">
         <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.01464824478628676</v>
+        <v>0.005908599449404933</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.003218958377605594</v>
+        <v>0.02356718796881335</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ2" t="n">
         <v>-0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.02910295133324822</v>
+        <v>0.1028810352145629</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.06160945795060888</v>
+        <v>-0.1980956411035548</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.06346280035528887</v>
+        <v>0.04266375782071439</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
@@ -1293,55 +1293,55 @@
         <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.03159391713659575</v>
+        <v>0.1714622755732922</v>
       </c>
       <c r="CX2" t="n">
         <v>-0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.02389457700439125</v>
+        <v>-0.001917582489432364</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.002725825012946287</v>
+        <v>-0.007476029124916119</v>
       </c>
       <c r="DA2" t="n">
         <v>-0</v>
       </c>
       <c r="DB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE2" t="n">
         <v>-0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.03764982877090165</v>
+        <v>0.06097601617382434</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.0241140576307954</v>
+        <v>-0.06591369651165642</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.02752073542778462</v>
+        <v>0.07192033985103984</v>
       </c>
       <c r="DJ2" t="n">
         <v>0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
         <v>-0</v>
@@ -1350,28 +1350,28 @@
         <v>-0</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.01583361300337519</v>
+        <v>0.09678852127000773</v>
       </c>
       <c r="DP2" t="n">
         <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.0730609548709788</v>
+        <v>-0.04068351344481089</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.04441029524461618</v>
+        <v>-0.1053244169918431</v>
       </c>
       <c r="DS2" t="n">
         <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
         <v>-0</v>
@@ -1380,43 +1380,43 @@
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.02475748232067152</v>
+        <v>0.07317911232457637</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.009866557565529403</v>
+        <v>-0.03358932408621342</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.0194466426991889</v>
+        <v>-0.2135720382175911</v>
       </c>
       <c r="EB2" t="n">
         <v>0</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF2" t="n">
         <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.02151702844159892</v>
+        <v>0.1439122612730026</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.08375347685187916</v>
+        <v>-0.127184170522172</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.06249611160263986</v>
+        <v>-0.07223925501729372</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
@@ -1425,7 +1425,7 @@
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
         <v>-0</v>
@@ -1434,19 +1434,19 @@
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.02732689672173665</v>
+        <v>0.1514016084132116</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.05271352491748541</v>
+        <v>-0.004327502047065017</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.0208501322478133</v>
+        <v>0.00245270447768002</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
         <v>0</v>
@@ -1455,76 +1455,76 @@
         <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX2" t="n">
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.02384157451425638</v>
+        <v>0.2030126758583594</v>
       </c>
       <c r="EZ2" t="n">
         <v>0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.01968171241820138</v>
+        <v>-0.01858090178811371</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.001258152351482244</v>
+        <v>0.004840227456524845</v>
       </c>
       <c r="FC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD2" t="n">
         <v>-0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.00624867786378639</v>
+        <v>0.197646607030364</v>
       </c>
       <c r="FI2" t="n">
         <v>0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.001504019357684276</v>
+        <v>-0.06631192735612018</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.04666068744010858</v>
+        <v>0.02670817690394653</v>
       </c>
       <c r="FL2" t="n">
         <v>0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.02887421200155625</v>
+        <v>0.2680412663712608</v>
       </c>
       <c r="FR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.006761150360827417</v>
+        <v>-0.3425815073492794</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.001189711286788366</v>
+        <v>-0.001995821401832814</v>
       </c>
       <c r="FU2" t="n">
         <v>0</v>
@@ -1533,28 +1533,28 @@
         <v>0</v>
       </c>
       <c r="FW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX2" t="n">
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.05896639299117197</v>
+        <v>0.1092675612732917</v>
       </c>
       <c r="GA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.02240035335631822</v>
+        <v>0.006510440912062125</v>
       </c>
       <c r="GC2" t="n">
         <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="GG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
